--- a/output/pdf_financials_xlsx/USCU.xlsx
+++ b/output/pdf_financials_xlsx/USCU.xlsx
@@ -1222,49 +1222,49 @@
         <v>-0.167552</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="17">
@@ -1506,49 +1506,49 @@
         <v>-0.167552</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="21">
@@ -1671,49 +1671,49 @@
         <v>-0.167552</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="24">
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>51.076967</v>
+        <v>-51.076967</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>94.87405</v>
+        <v>-94.87405</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>9.002649999999999</v>
+        <v>-9.002649999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.2098</v>
+        <v>-9.2098</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>27.7015</v>
+        <v>-27.7015</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>29.5918</v>
+        <v>-29.5918</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>36.782625</v>
+        <v>-36.782625</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>120.5464</v>
+        <v>-120.5464</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1911,49 +1911,49 @@
         <v>-0.167552</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="28">
@@ -2021,49 +2021,49 @@
         <v>-0.167552</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="30">
@@ -2163,49 +2163,49 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5666,49 +5666,49 @@
         <v>0.562393</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.145681</v>
+        <v>0.562393</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.820288</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.1086</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.1286</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.7231</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.6548</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.5806</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.6246</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.2581</v>
       </c>
     </row>
     <row r="93">
@@ -7074,13 +7074,13 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.694295</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.1298</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -7089,13 +7089,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -7104,19 +7104,19 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.05975</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.04125</v>
       </c>
     </row>
     <row r="119">
@@ -9152,7 +9152,11 @@
           <t>Reserve for warrants (Note 13)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10082,7 +10086,11 @@
           <t>Reserve for warrants (Note 14)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10620,7 +10628,11 @@
           <t>Reserve for warrants (Note 11)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11160,7 +11172,11 @@
           <t>Reserve for warrants (Note 12)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13538,7 +13554,11 @@
           <t>Reserve for warrants (Note 13) 820,288</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15654,7 +15674,11 @@
           <t>Marketable securities received for sale of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -18782,7 +18806,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -21530,7 +21558,11 @@
           <t>Write-down (Recovery) of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -22298,7 +22330,11 @@
           <t>Shares issued for exploration and evaluation expenditures (Note 12 (a))</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -22392,7 +22428,11 @@
           <t>Write-down of exploration and evaluation expenditures (Note 9)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -22582,7 +22622,11 @@
           <t>Sale of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25901,25 +25945,25 @@
         </is>
       </c>
       <c r="N191" s="5" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>0.346118</v>
+        <v>-0.346118</v>
       </c>
       <c r="P191" s="5" t="n">
-        <v>2.410928</v>
+        <v>-2.410928</v>
       </c>
       <c r="Q191" s="5" t="n">
-        <v>0.677671</v>
+        <v>-0.677671</v>
       </c>
       <c r="R191" s="5" t="n">
-        <v>1.648993</v>
+        <v>-1.648993</v>
       </c>
       <c r="S191" s="5" t="n">
-        <v>0.890433</v>
+        <v>-0.890433</v>
       </c>
       <c r="T191" s="5" t="n">
-        <v>1.134001</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="192">
@@ -27866,16 +27910,16 @@
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>0.55403</v>
+        <v>-0.55403</v>
       </c>
       <c r="M213" s="5" t="n">
-        <v>0.887754</v>
+        <v>-0.887754</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>1.471305</v>
+        <v>-1.471305</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -31808,13 +31852,13 @@
         </is>
       </c>
       <c r="I255" s="5" t="n">
-        <v>0.5401589999999999</v>
+        <v>-0.5401589999999999</v>
       </c>
       <c r="J255" s="5" t="n">
-        <v>0.276294</v>
+        <v>-0.276294</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>0.070938</v>
+        <v>-0.070938</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -34526,10 +34570,10 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="H284" s="5" t="n">
-        <v>1.009537</v>
+        <v>-1.009537</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -35739,10 +35783,10 @@
         </is>
       </c>
       <c r="F297" s="5" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="G297" s="5" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -36311,10 +36355,10 @@
         </is>
       </c>
       <c r="F303" s="5" t="n">
-        <v>1.532309</v>
+        <v>-1.532309</v>
       </c>
       <c r="G303" s="5" t="n">
-        <v>1.897481</v>
+        <v>-1.897481</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/USCU.xlsx
+++ b/output/pdf_financials_xlsx/USCU.xlsx
@@ -2309,37 +2309,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.405951</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.405951</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.158339</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.181083</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.055907</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007974</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.235432</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.332425</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.01236</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>2.53178</v>
@@ -2419,37 +2419,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.405951</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.25475</v>
+        <v>0.660701</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.158339</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.181083</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.055907</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007974</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.070034</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.235432</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.332425</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.01236</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>2.56378</v>
@@ -3079,31 +3079,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.444053</v>
+        <v>0.038102</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.418143</v>
+        <v>0.012192</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.173736</v>
+        <v>0.015397</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.239068</v>
+        <v>0.057985</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.07739699999999999</v>
+        <v>0.02149</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.020869</v>
+        <v>0.012895</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005864</v>
+        <v>0.00583</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.264066</v>
+        <v>0.028634</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.398302</v>
+        <v>0.065877</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/USCU.xlsx
+++ b/output/pdf_financials_xlsx/USCU.xlsx
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.726024</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>1.653969</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -24082,7 +24082,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E171" s="5" t="n">
         <v>0.726024</v>
       </c>

--- a/output/pdf_financials_xlsx/USCU.xlsx
+++ b/output/pdf_financials_xlsx/USCU.xlsx
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.167552</v>
+        <v>-0.161552</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.532309</v>
+        <v>-1.454309</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.897481</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.006</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.078</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.167552</v>
+        <v>-0.161552</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.532309</v>
+        <v>-1.454309</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.897481</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.167552</v>
+        <v>-0.161552</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.532309</v>
+        <v>-1.454309</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.897481</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.713974447855799</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.363371883141753</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.15868</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T327"/>
+  <dimension ref="A1:T329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16064,10 +16064,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J86" s="5" t="n">
+        <v>0.017512</v>
       </c>
       <c r="K86" s="5" t="n">
         <v>-0.03137</v>
@@ -17420,10 +17418,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J101" s="5" t="n">
+        <v>0.008595</v>
       </c>
       <c r="K101" s="5" t="n">
         <v>0.007065</v>
@@ -17692,10 +17688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J104" s="5" t="n">
+        <v>0.006017</v>
       </c>
       <c r="K104" s="5" t="n">
         <v>-0.001697</v>
@@ -18352,10 +18346,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J111" s="5" t="n">
+        <v>-0.240183</v>
       </c>
       <c r="K111" s="5" t="n">
         <v>-0.15594</v>
@@ -18446,15 +18438,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J112" s="5" t="n">
+        <v>-0.047933</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>-0.007939999999999999</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -18544,15 +18532,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J113" s="5" t="n">
+        <v>0.055907</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>0.007974</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -18642,15 +18626,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J114" s="5" t="n">
+        <v>0.007974</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>3.4e-05</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -20114,7 +20094,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -20296,12 +20280,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>TTORONTO, Caanada</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Interest accretion on convertible debentures</t>
+          <t>MMarch</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -20325,16 +20309,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="5" t="n">
-        <v>0.004063</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.003987</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020166</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>2.3e-05</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -20395,7 +20379,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery</t>
+          <t>Unrealized gain on marketable securities</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -20414,21 +20398,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="5" t="n">
-        <v>-0.161</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>-0.006</v>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K133" s="5" t="n">
+        <v>-0.01</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -20489,7 +20475,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Loss on disposition of available-for-sale investments</t>
+          <t>Interest accretion on convertible debentures</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -20514,12 +20500,10 @@
         </is>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.007377</v>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004063</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>0.003987</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -20580,19 +20564,15 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Trade and other receivables</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Redemption of convertible debentures</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -20613,11 +20593,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>0.012663</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0.006017</v>
+        <v>-0.101</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -20678,19 +20660,15 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital</t>
+          <t>Supplementary Information</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Conversion of convertible debentures</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -20711,11 +20689,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="5" t="n">
-        <v>0.036495</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0.008595</v>
+        <v>0.024</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -20776,19 +20756,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Trade and other payables</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Flow-through share premium recovery</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -20804,16 +20780,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>-0.161</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>-0.008817999999999999</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>0.017512</v>
+        <v>-0.006</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -20874,19 +20850,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Loss on disposition of available-for-sale investments</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -20908,10 +20880,12 @@
         </is>
       </c>
       <c r="I138" s="5" t="n">
-        <v>-0.407049</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>-0.240183</v>
+        <v>0.007377</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -20972,15 +20946,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Net change in non-cash working capital</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Issuance of convertible debentures, net of costs</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -21002,12 +20980,10 @@
         </is>
       </c>
       <c r="I139" s="5" t="n">
-        <v>0.11815</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012663</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>0.006017</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -21068,15 +21044,19 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Net change in non-cash working capital</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Redemption of convertible debentures</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -21097,13 +21077,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="5" t="n">
+        <v>0.036495</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>-0.101</v>
+        <v>0.008595</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -21164,15 +21142,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Net change in non-cash working capital</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sale of available-for-sale investments</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -21194,12 +21176,10 @@
         </is>
       </c>
       <c r="I141" s="5" t="n">
-        <v>0.045123</v>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008817999999999999</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>0.017512</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -21260,17 +21240,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Net change in non-cash working capital</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Net decrease in cash</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -21294,10 +21274,10 @@
         </is>
       </c>
       <c r="I142" s="5" t="n">
-        <v>-0.125176</v>
+        <v>-0.407049</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>-0.047933</v>
+        <v>-0.240183</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -21358,12 +21338,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Supplementary Information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Conversion of convertible debentures</t>
+          <t>Issuance of convertible debentures, net of costs</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -21387,13 +21367,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="n">
-        <v>0.024</v>
+      <c r="I143" s="5" t="n">
+        <v>0.11815</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -21454,37 +21434,37 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Sale of available-for-sale investments</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n">
-        <v>-1.532309</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>-1.897481</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>-1.009537</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>0.045123</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -21550,17 +21530,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Write-down (Recovery) of exploration and evaluation expenditures</t>
+          <t>Net decrease in cash</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -21573,21 +21553,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G145" s="5" t="n">
-        <v>0.613826</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>-0.1298</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-0.125176</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>-0.047933</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -21653,27 +21633,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Gain on sale of subsidiary</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" s="5" t="n">
+        <v>-1.532309</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-1.897481</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>-1e-05</v>
+        <v>-1.009537</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -21749,23 +21729,29 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange differences</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Write-down (Recovery) of exploration and evaluation expenditures</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F147" s="5" t="n">
-        <v>0.012125</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.000933</v>
+        <v>0.613826</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>-0.002674</v>
+        <v>-0.1298</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -21836,19 +21822,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dividends paid (Note 9)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>CashDividendsPaid</t>
-        </is>
-      </c>
+          <t>Gain on sale of subsidiary</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -21865,7 +21847,7 @@
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>-3.65</v>
+        <v>-1e-05</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -21936,34 +21918,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cash provided from (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange differences</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F149" s="5" t="n">
+        <v>0.012125</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.000933</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>-3.184653</v>
+        <v>-0.002674</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -22034,15 +22010,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sale of exploration and evaluation expenditures, net of costs</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Dividends paid (Note 9)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -22053,11 +22033,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G150" s="5" t="n">
-        <v>0.1</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>4.388857</v>
+        <v>-3.65</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -22128,15 +22110,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Proceeds on sale of subsidiary</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Cash provided from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -22147,13 +22133,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>0.5024999999999999</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>1e-05</v>
+        <v>-3.184653</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -22224,34 +22208,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Share based payments (Note 12 (c))</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Sale of exploration and evaluation expenditures, net of costs</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0.106</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>4.388857</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -22322,34 +22302,32 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation expenditures (Note 12 (a))</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Proceeds on sale of subsidiary</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.09080000000000001</v>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>0.080469</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -22425,12 +22403,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation expenditures (Note 9)</t>
+          <t>Share based payments (Note 12 (c))</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -22438,13 +22416,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F154" s="5" t="n">
+        <v>0.106</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.613826</v>
+        <v>0.025</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -22520,25 +22496,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Issuance of share capital, net of costs (Note 12 (a))</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Shares issued for exploration and evaluation expenditures (Note 12 (a))</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1.653969</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.080469</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -22614,12 +22594,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sale of exploration and evaluation expenditures</t>
+          <t>Write-down of exploration and evaluation expenditures (Note 9)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22638,7 +22618,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.1</v>
+        <v>0.613826</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -22714,12 +22694,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cash acquired on corporate merger</t>
+          <t>Issuance of share capital, net of costs (Note 12 (a))</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -22729,12 +22709,10 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.016595</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.653969</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.5024999999999999</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -22815,12 +22793,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>(Decrease) Increase in cash</t>
+          <t>Sale of exploration and evaluation expenditures</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -22828,11 +22806,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F158" s="5" t="n">
-        <v>0.241016</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>-0.488628</v>
+        <v>0.1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -22908,12 +22888,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>the classification and measurement of financial instruments.</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>• IFRS 11 ‘Joint Arrangements’ - effective for annual periods beginning on or after January</t>
+          <t>Cash acquired on corporate merger</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -22923,10 +22903,12 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0.002013</v>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.016595</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -23002,29 +22984,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>(Decrease) Increase in cash</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="n">
-        <v>-0.167552</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>-1.076626</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.241016</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-0.488628</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -23100,12 +23082,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>from operating activities</t>
+          <t>the classification and measurement of financial instruments.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties and related deferred costs</t>
+          <t>• IFRS 11 ‘Joint Arrangements’ - effective for annual periods beginning on or after January</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -23115,12 +23097,10 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>0.413664</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002013</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -23196,22 +23176,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>from operating activities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral properties</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>-0.167552</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.060266</v>
+        <v>-1.076626</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -23297,21 +23279,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Write-off of mineral properties and related deferred costs</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.106</v>
+        <v>0.413664</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -23397,21 +23375,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Gain on disposal of mineral properties</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.000763</v>
+        <v>-0.060266</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -23497,17 +23471,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange losses</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0.007561</v>
+        <v>0.106</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -23593,15 +23571,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Future income tax recovery</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>-0.006</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.078</v>
+        <v>0.000763</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -23682,24 +23666,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>from operating activities</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n">
-        <v>-0.039724</v>
+          <t>Unrealized foreign exchange losses</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.009629</v>
+        <v>0.007561</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -23780,24 +23762,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>from operating activities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Future income tax recovery</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.038102</v>
+        <v>-0.006</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.100803</v>
+        <v>-0.078</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -23883,19 +23865,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Accounts payable and accured liabilities</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0.00411</v>
+        <v>-0.039724</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>-0.217359</v>
+        <v>0.009629</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -23981,19 +23963,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cash flow used in operating activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.247268</v>
+        <v>-0.038102</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.793831</v>
+        <v>0.100803</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -24074,24 +24056,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Issue of common shares, net of issue costs</t>
+          <t>Accounts payable and accured liabilities</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0.726024</v>
+        <v>0.00411</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>1.653969</v>
+        <v>-0.217359</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -24172,22 +24154,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Cash flow used in operating activities</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
-        <v>-0.126734</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.247268</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>-0.793831</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -24273,16 +24257,16 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cash flow provided from financing activities</t>
+          <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>IssuanceOfCapitalStock</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0.59929</v>
+        <v>0.726024</v>
       </c>
       <c r="F173" s="5" t="n">
         <v>1.653969</v>
@@ -24366,20 +24350,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cash acquired on corporate merger (Note 5)</t>
+          <t>Transaction costs</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="n">
-        <v>0.32344</v>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>0.016595</v>
+        <v>-0.126734</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -24460,22 +24446,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Proceeds on disposition of mineral properties</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flow provided from financing activities</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>0.59929</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>0.12</v>
+        <v>1.653969</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -24561,15 +24549,15 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Acquisitions of mineral properties and related deferred costs</t>
+          <t>Cash acquired on corporate merger (Note 5)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" s="5" t="n">
-        <v>-1.085797</v>
+        <v>0.32344</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.755717</v>
+        <v>0.016595</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -24655,19 +24643,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Cash flow used in investing activities</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="n">
-        <v>-0.762357</v>
+          <t>Proceeds on disposition of mineral properties</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F177" s="5" t="n">
-        <v>-0.619122</v>
+        <v>0.12</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -24753,19 +24739,15 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Net increase in cash</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Acquisitions of mineral properties and related deferred costs</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" s="5" t="n">
-        <v>-0.410335</v>
+        <v>-1.085797</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.241016</v>
+        <v>-0.755717</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -24851,19 +24833,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash flow used in investing activities</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0.816286</v>
+        <v>-0.762357</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>0.405951</v>
+        <v>-0.619122</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -24949,19 +24931,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Net increase in cash</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0.405951</v>
+        <v>-0.410335</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>0.646967</v>
+        <v>0.241016</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -25042,20 +25024,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Changes in non-cash investing and financing activites</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Shares issued for purchase of mineral properties $</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E181" s="5" t="n">
-        <v>0.25875</v>
+        <v>0.816286</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>0.062</v>
+        <v>0.405951</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -25136,22 +25122,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Changes in non-cash investing and financing activites</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Warrants issued for purchase of mineral properties $</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.405951</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>0.646967</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -25237,15 +25225,15 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of accounts payable and accruals $</t>
+          <t>Shares issued for purchase of mineral properties $</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" s="5" t="n">
-        <v>0.12</v>
+        <v>0.25875</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.062</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -25321,24 +25309,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing and financing activites</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Warrants issued for purchase of mineral properties $</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" s="5" t="n">
+        <v>0.079</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -25370,60 +25356,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L184" s="5" t="n">
-        <v>0.02844</v>
-      </c>
-      <c r="M184" s="5" t="n">
-        <v>0.02824</v>
-      </c>
-      <c r="N184" s="5" t="n">
-        <v>0.035843</v>
-      </c>
-      <c r="O184" s="5" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="P184" s="5" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q184" s="5" t="n">
-        <v>0.05126</v>
-      </c>
-      <c r="R184" s="5" t="n">
-        <v>0.05124</v>
-      </c>
-      <c r="S184" s="5" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="T184" s="5" t="n">
-        <v>0.05244</v>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Changes in non-cash investing and financing activites</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for settlement of accounts payable and accruals $</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>0.0288</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -25445,14 +25445,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K185" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L185" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M185" s="5" t="n">
-        <v>0.030941</v>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -25469,17 +25475,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q185" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R185" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S185" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T185" s="5" t="n">
-        <v>0.06</v>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -25491,10 +25505,14 @@
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 12 (c) and 14)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -25530,46 +25548,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L186" s="5" t="n">
+        <v>0.02844</v>
+      </c>
+      <c r="M186" s="5" t="n">
+        <v>0.02824</v>
+      </c>
+      <c r="N186" s="5" t="n">
+        <v>0.035843</v>
+      </c>
+      <c r="O186" s="5" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="P186" s="5" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="Q186" s="5" t="n">
+        <v>0.05126</v>
       </c>
       <c r="R186" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05124</v>
+      </c>
+      <c r="S186" s="5" t="n">
+        <v>0.051</v>
       </c>
       <c r="T186" s="5" t="n">
-        <v>0.261</v>
+        <v>0.05244</v>
       </c>
     </row>
     <row r="187">
@@ -25581,12 +25585,12 @@
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Office, general and administration</t>
+          <t>Management and consulting fees (Note 11)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -25594,14 +25598,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>0.096114</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>0.087481</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>0.049927</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -25614,34 +25624,40 @@
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>0.020523</v>
+        <v>0.024</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.03</v>
       </c>
       <c r="M187" s="5" t="n">
-        <v>0.040334</v>
-      </c>
-      <c r="N187" s="5" t="n">
-        <v>0.043717</v>
-      </c>
-      <c r="O187" s="5" t="n">
-        <v>0.028738</v>
-      </c>
-      <c r="P187" s="5" t="n">
-        <v>0.127872</v>
+        <v>0.030941</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q187" s="5" t="n">
-        <v>-0.010797</v>
+        <v>0.06</v>
       </c>
       <c r="R187" s="5" t="n">
-        <v>0.038378</v>
+        <v>0.06</v>
       </c>
       <c r="S187" s="5" t="n">
-        <v>0.050707</v>
+        <v>0.06</v>
       </c>
       <c r="T187" s="5" t="n">
-        <v>0.075892</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="188">
@@ -25653,7 +25669,7 @@
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Investors relations, promotion and travel</t>
+          <t>Share-based payments (Notes 12 (c) and 14)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -25687,35 +25703,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K188" s="5" t="n">
-        <v>0.022092</v>
-      </c>
-      <c r="L188" s="5" t="n">
-        <v>0.087299</v>
-      </c>
-      <c r="M188" s="5" t="n">
-        <v>0.122991</v>
-      </c>
-      <c r="N188" s="5" t="n">
-        <v>0.364695</v>
-      </c>
-      <c r="O188" s="5" t="n">
-        <v>0.03179</v>
-      </c>
-      <c r="P188" s="5" t="n">
-        <v>0.489558</v>
-      </c>
-      <c r="Q188" s="5" t="n">
-        <v>0.238345</v>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R188" s="5" t="n">
-        <v>0.08878</v>
-      </c>
-      <c r="S188" s="5" t="n">
-        <v>0.09098100000000001</v>
+        <v>0.132</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T188" s="5" t="n">
-        <v>0.366895</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="189">
@@ -25727,29 +25759,27 @@
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 10)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Office, general and administration</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F189" s="5" t="n">
+        <v>0.096114</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.087481</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.049927</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -25761,43 +25791,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K189" s="5" t="n">
+        <v>0.020523</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>0.431295</v>
+        <v>0.0356</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>0.545453</v>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.040334</v>
+      </c>
+      <c r="N189" s="5" t="n">
+        <v>0.043717</v>
+      </c>
+      <c r="O189" s="5" t="n">
+        <v>0.028738</v>
+      </c>
+      <c r="P189" s="5" t="n">
+        <v>0.127872</v>
       </c>
       <c r="Q189" s="5" t="n">
-        <v>0.281863</v>
+        <v>-0.010797</v>
       </c>
       <c r="R189" s="5" t="n">
-        <v>1.198095</v>
+        <v>0.038378</v>
       </c>
       <c r="S189" s="5" t="n">
-        <v>0.586745</v>
+        <v>0.050707</v>
       </c>
       <c r="T189" s="5" t="n">
-        <v>0.366274</v>
+        <v>0.075892</v>
       </c>
     </row>
     <row r="190">
@@ -25809,7 +25831,7 @@
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Change of fair value on marketable securities (Note 6)</t>
+          <t>Investors relations, promotion and travel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -25843,47 +25865,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K190" s="5" t="n">
+        <v>0.022092</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>0.087299</v>
+      </c>
+      <c r="M190" s="5" t="n">
+        <v>0.122991</v>
+      </c>
+      <c r="N190" s="5" t="n">
+        <v>0.364695</v>
+      </c>
+      <c r="O190" s="5" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="P190" s="5" t="n">
+        <v>0.489558</v>
       </c>
       <c r="Q190" s="5" t="n">
-        <v>0.042</v>
+        <v>0.238345</v>
       </c>
       <c r="R190" s="5" t="n">
-        <v>0.0805</v>
+        <v>0.08878</v>
       </c>
       <c r="S190" s="5" t="n">
-        <v>0.051</v>
+        <v>0.09098100000000001</v>
       </c>
       <c r="T190" s="5" t="n">
-        <v>-0.0485</v>
+        <v>0.366895</v>
       </c>
     </row>
     <row r="191">
@@ -25895,14 +25905,10 @@
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (Note 10)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -25938,36 +25944,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N191" s="5" t="n">
-        <v>-1.471305</v>
-      </c>
-      <c r="O191" s="5" t="n">
-        <v>-0.346118</v>
-      </c>
-      <c r="P191" s="5" t="n">
-        <v>-2.410928</v>
+      <c r="L191" s="5" t="n">
+        <v>0.431295</v>
+      </c>
+      <c r="M191" s="5" t="n">
+        <v>0.545453</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q191" s="5" t="n">
-        <v>-0.677671</v>
+        <v>0.281863</v>
       </c>
       <c r="R191" s="5" t="n">
-        <v>-1.648993</v>
+        <v>1.198095</v>
       </c>
       <c r="S191" s="5" t="n">
-        <v>-0.890433</v>
+        <v>0.586745</v>
       </c>
       <c r="T191" s="5" t="n">
-        <v>-1.134001</v>
+        <v>0.366274</v>
       </c>
     </row>
     <row r="192">
@@ -25979,14 +25987,10 @@
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Change of fair value on marketable securities (Note 6)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -26032,26 +26036,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N192" s="5" t="n">
-        <v>4e-08</v>
-      </c>
-      <c r="O192" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="P192" s="5" t="n">
-        <v>2e-08</v>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q192" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.042</v>
       </c>
       <c r="R192" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.0805</v>
       </c>
       <c r="S192" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.051</v>
       </c>
       <c r="T192" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.0485</v>
       </c>
     </row>
     <row r="193">
@@ -26060,17 +26070,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Weighted average number</t>
-        </is>
-      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares - basic and diluted (000’s)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -26081,11 +26091,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G193" s="5" t="n">
-        <v>0.083833</v>
-      </c>
-      <c r="H193" s="5" t="n">
-        <v>0.08805</v>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -26097,35 +26111,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K193" s="5" t="n">
-        <v>0.014644</v>
-      </c>
-      <c r="L193" s="5" t="n">
-        <v>0.022969</v>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v>0.029571</v>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N193" s="5" t="n">
-        <v>0.038651</v>
+        <v>-1.471305</v>
       </c>
       <c r="O193" s="5" t="n">
-        <v>0.043166</v>
+        <v>-0.346118</v>
       </c>
       <c r="P193" s="5" t="n">
-        <v>0.104583</v>
+        <v>-2.410928</v>
       </c>
       <c r="Q193" s="5" t="n">
-        <v>0.112155</v>
+        <v>-0.677671</v>
       </c>
       <c r="R193" s="5" t="n">
-        <v>0.114201</v>
+        <v>-1.648993</v>
       </c>
       <c r="S193" s="5" t="n">
-        <v>0.117431</v>
+        <v>-0.890433</v>
       </c>
       <c r="T193" s="5" t="n">
-        <v>0.138616</v>
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="194">
@@ -26134,17 +26154,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Weighted average number</t>
-        </is>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Total 634,086 193,860 - (890,433) (62,487) 2,366,237 - 213,800 - 7,500 - 10,240 261,000 -</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -26190,36 +26210,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N194" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="O194" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="P194" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+      <c r="Q194" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="R194" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="S194" s="5" t="n">
-        <v>1.662289</v>
+        <v>1e-08</v>
       </c>
       <c r="T194" s="5" t="n">
-        <v>-1.134001</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="195">
@@ -26235,7 +26245,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Total 2,001,079 150,000 132,000 - (1,648,993) 634,086 193,860 -</t>
+          <t>Weighted average number of common shares - basic and diluted (000’s)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -26249,15 +26259,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G195" s="5" t="n">
+        <v>0.083833</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>0.08805</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -26269,51 +26275,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K195" s="5" t="n">
+        <v>0.014644</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>0.022969</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>0.029571</v>
+      </c>
+      <c r="N195" s="5" t="n">
+        <v>0.038651</v>
+      </c>
+      <c r="O195" s="5" t="n">
+        <v>0.043166</v>
+      </c>
+      <c r="P195" s="5" t="n">
+        <v>0.104583</v>
+      </c>
+      <c r="Q195" s="5" t="n">
+        <v>0.112155</v>
       </c>
       <c r="R195" s="5" t="n">
-        <v>-0.062487</v>
+        <v>0.114201</v>
       </c>
       <c r="S195" s="5" t="n">
-        <v>-0.890433</v>
-      </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.117431</v>
+      </c>
+      <c r="T195" s="5" t="n">
+        <v>0.138616</v>
       </c>
     </row>
     <row r="196">
@@ -26322,10 +26312,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Weighted average number</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 12 (c) and 14)</t>
+          <t>Total 634,086 193,860 - (890,433) (62,487) 2,366,237 - 213,800 - 7,500 - 10,240 261,000 -</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -26389,21 +26383,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q196" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R196" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S196" s="5" t="n">
+        <v>1.662289</v>
+      </c>
+      <c r="T196" s="5" t="n">
+        <v>-1.134001</v>
       </c>
     </row>
     <row r="197">
@@ -26419,7 +26413,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Total 2,663,750 15,000 - (677,671) 2,001,079 150,000 132,000 -</t>
+          <t>Total 2,001,079 150,000 132,000 - (1,648,993) 634,086 193,860 -</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -26483,16 +26477,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q197" s="5" t="n">
-        <v>0.634086</v>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R197" s="5" t="n">
-        <v>-1.648993</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.062487</v>
+      </c>
+      <c r="S197" s="5" t="n">
+        <v>-0.890433</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -26506,14 +26500,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Warrants   723,100          (68,300)         654,800 (11,800)          (62,400)         580,600                                                                                                                                                                                                              financial</t>
-        </is>
-      </c>
+      <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Amount 161,800 these 16,813,483</t>
+          <t>Share based payments (Notes 12 (c) and 14)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -26578,10 +26568,10 @@
         </is>
       </c>
       <c r="Q198" s="5" t="n">
-        <v>16.975283</v>
+        <v>0.015</v>
       </c>
       <c r="R198" s="5" t="n">
-        <v>16.813483</v>
+        <v>0.132</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -26602,12 +26592,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Share integral Number shares 112,154,62 112,154,62</t>
+          <t>Total 2,663,750 15,000 - (677,671) 2,001,079 150,000 132,000 -</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -26672,10 +26662,10 @@
         </is>
       </c>
       <c r="Q199" s="5" t="n">
-        <v>115.154627</v>
+        <v>0.634086</v>
       </c>
       <c r="R199" s="5" t="n">
-        <v>3</v>
+        <v>-1.648993</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -26694,17 +26684,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Warrants   723,100          (68,300)         654,800 (11,800)          (62,400)         580,600                                                                                                                                                                                                              financial</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 12)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Amount 161,800 these 16,813,483</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -26760,16 +26750,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P200" s="5" t="n">
-        <v>0.063166</v>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q200" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.975283</v>
+      </c>
+      <c r="R200" s="5" t="n">
+        <v>16.813483</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -26788,10 +26778,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 13 (c) and 15)</t>
+          <t>Share integral Number shares 112,154,62 112,154,62</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -26850,16 +26844,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P201" s="5" t="n">
-        <v>0.22</v>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q201" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>115.154627</v>
+      </c>
+      <c r="R201" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -26881,10 +26875,14 @@
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 11)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Management and consulting fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -26941,10 +26939,10 @@
         </is>
       </c>
       <c r="P202" s="5" t="n">
-        <v>1.487332</v>
+        <v>0.063166</v>
       </c>
       <c r="Q202" s="5" t="n">
-        <v>0.281863</v>
+        <v>0.06</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -26971,7 +26969,7 @@
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Forgiveness of CEBA loan (Note 10)</t>
+          <t>Share based payments (Notes 13 (c) and 15)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -27031,12 +27029,10 @@
         </is>
       </c>
       <c r="P203" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.22</v>
+      </c>
+      <c r="Q203" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -27063,7 +27059,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities (Note 6)</t>
+          <t>Exploration and evaluation expenditures (Note 11)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -27102,8 +27098,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L204" s="5" t="n">
-        <v>0.01</v>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -27120,13 +27118,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P204" s="5" t="n">
+        <v>1.487332</v>
       </c>
       <c r="Q204" s="5" t="n">
-        <v>0.042</v>
+        <v>0.281863</v>
       </c>
       <c r="R204" t="inlineStr">
         <is>
@@ -27153,14 +27149,10 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Forgiveness of CEBA loan (Note 10)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -27206,16 +27198,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N205" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="O205" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P205" s="5" t="n">
+        <v>-0.02</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
@@ -27247,7 +27241,7 @@
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 9, 10 (c) and 12)</t>
+          <t>Unrealized loss on marketable securities (Note 6)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -27286,31 +27280,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L206" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N206" s="5" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="O206" s="5" t="n">
-        <v>0.025</v>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q206" s="5" t="n">
+        <v>0.042</v>
       </c>
       <c r="R206" t="inlineStr">
         <is>
@@ -27337,10 +27331,14 @@
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 8)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Management and consulting fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -27387,10 +27385,10 @@
         </is>
       </c>
       <c r="N207" s="5" t="n">
-        <v>0.81885</v>
+        <v>0.045</v>
       </c>
       <c r="O207" s="5" t="n">
-        <v>0.17149</v>
+        <v>0.06</v>
       </c>
       <c r="P207" t="inlineStr">
         <is>
@@ -27427,14 +27425,10 @@
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based payments (Notes 9, 10 (c) and 12)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -27445,11 +27439,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G208" s="5" t="n">
-        <v>0.10564</v>
-      </c>
-      <c r="H208" s="5" t="n">
-        <v>0.06</v>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -27471,16 +27469,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M208" s="5" t="n">
-        <v>0.030941</v>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N208" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1632</v>
+      </c>
+      <c r="O208" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="P208" t="inlineStr">
         <is>
@@ -27517,7 +27515,7 @@
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 10, 11(c) and 13)</t>
+          <t>Exploration and evaluation expenditures (Note 8)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -27561,16 +27559,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M209" s="5" t="n">
-        <v>0.1188</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N209" s="5" t="n">
-        <v>0.1632</v>
-      </c>
-      <c r="O209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.81885</v>
+      </c>
+      <c r="O209" s="5" t="n">
+        <v>0.17149</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -27607,23 +27605,29 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 9)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Management and consulting fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F210" s="5" t="n">
-        <v>0.726517</v>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>0.793672</v>
+        <v>0.10564</v>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.747177</v>
+        <v>0.06</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -27646,10 +27650,10 @@
         </is>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0.545453</v>
+        <v>0.030941</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>0.81885</v>
+        <v>0.045</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -27691,7 +27695,7 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Realized gain on available-for-sale investments (Note 7)</t>
+          <t>Share based payments (Notes 10, 11(c) and 13)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -27736,12 +27740,10 @@
         </is>
       </c>
       <c r="M211" s="5" t="n">
-        <v>-0.006985</v>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1188</v>
+      </c>
+      <c r="N211" s="5" t="n">
+        <v>0.1632</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -27783,7 +27785,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 7)</t>
+          <t>Exploration and evaluation expenditures (Note 9)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -27792,20 +27794,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F212" s="5" t="n">
+        <v>0.726517</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.793672</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>0.747177</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -27828,12 +27824,10 @@
         </is>
       </c>
       <c r="M212" s="5" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.545453</v>
+      </c>
+      <c r="N212" s="5" t="n">
+        <v>0.81885</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -27875,14 +27869,10 @@
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Realized gain on available-for-sale investments (Note 7)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -27913,17 +27903,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K213" s="5" t="n">
-        <v>-0.070938</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>-0.55403</v>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M213" s="5" t="n">
-        <v>-0.887754</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>-1.471305</v>
+        <v>-0.006985</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -27962,14 +27958,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Items that will be reclassified subsequently to loss</t>
-        </is>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Change in unrealized loss on available-for-sale investments (Note 7)</t>
+          <t>Impairment of available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -28014,7 +28006,7 @@
         </is>
       </c>
       <c r="M214" s="5" t="n">
-        <v>0.012225</v>
+        <v>0.007979999999999999</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
@@ -28058,17 +28050,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Items that will be reclassified subsequently to loss</t>
-        </is>
-      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Realized gain on available-for-sale investments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -28099,23 +28091,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K215" s="5" t="n">
+        <v>-0.070938</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>-0.55403</v>
       </c>
       <c r="M215" s="5" t="n">
-        <v>0.006985</v>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.887754</v>
+      </c>
+      <c r="N215" s="5" t="n">
+        <v>-1.471305</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -28161,7 +28147,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 7)</t>
+          <t>Change in unrealized loss on available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -28206,7 +28192,7 @@
         </is>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.007979999999999999</v>
+        <v>0.012225</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -28257,7 +28243,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Realized gain on available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -28302,7 +28288,7 @@
         </is>
       </c>
       <c r="M217" s="5" t="n">
-        <v>0.02719</v>
+        <v>0.006985</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -28353,7 +28339,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Impairment of available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -28398,10 +28384,12 @@
         </is>
       </c>
       <c r="M218" s="5" t="n">
-        <v>0.914944</v>
-      </c>
-      <c r="N218" s="5" t="n">
-        <v>1.471305</v>
+        <v>0.007979999999999999</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -28447,14 +28435,10 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -28496,10 +28480,12 @@
         </is>
       </c>
       <c r="M219" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="N219" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.02719</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -28538,10 +28524,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Items that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 12(c) and 14)</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -28575,19 +28565,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K220" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>0.031</v>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M220" s="5" t="n">
-        <v>0.1188</v>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.914944</v>
+      </c>
+      <c r="N220" s="5" t="n">
+        <v>1.471305</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -28626,15 +28618,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Items that will be reclassified subsequently to loss</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain)</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -28672,18 +28668,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L221" s="5" t="n">
-        <v>-0.000924</v>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="N221" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -28725,7 +28719,7 @@
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Realized (gain) on marketable securities and available-for-sale investments (Notes 6 and 8)</t>
+          <t>Share based payments (Notes 12(c) and 14)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -28759,16 +28753,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K222" s="5" t="n">
+        <v>0.011</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>-0.09868</v>
+        <v>0.031</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>-0.006985</v>
+        <v>0.1188</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
@@ -28815,10 +28807,14 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 8)</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>Foreign exchange (gain)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -28854,13 +28850,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M223" s="5" t="n">
-        <v>0.007979999999999999</v>
+      <c r="L223" s="5" t="n">
+        <v>-0.000924</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -28904,14 +28900,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Other Comprehensive loss (Income)</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Change in unrealized loss (gain) on available-for-sale investments (Note 8)</t>
+          <t>Realized (gain) on marketable securities and available-for-sale investments (Notes 6 and 8)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -28951,10 +28943,10 @@
         </is>
       </c>
       <c r="L224" s="5" t="n">
-        <v>-0.01377</v>
+        <v>-0.09868</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.012225</v>
+        <v>-0.006985</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -28998,14 +28990,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Other Comprehensive loss (Income)</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Realized (gain) on available-for-sale investments (Note 8)</t>
+          <t>Impairment of available-for-sale investments (Note 8)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -29050,7 +29038,7 @@
         </is>
       </c>
       <c r="M225" s="5" t="n">
-        <v>0.006985</v>
+        <v>0.007979999999999999</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -29101,7 +29089,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 8)</t>
+          <t>Change in unrealized loss (gain) on available-for-sale investments (Note 8)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -29140,13 +29128,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L226" s="5" t="n">
+        <v>-0.01377</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.007979999999999999</v>
+        <v>0.012225</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -29197,7 +29183,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Other comprehensive loss (income)</t>
+          <t>Realized (gain) on available-for-sale investments (Note 8)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -29236,11 +29222,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L227" s="5" t="n">
-        <v>-0.01377</v>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M227" s="5" t="n">
-        <v>0.02719</v>
+        <v>0.006985</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -29291,7 +29279,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Impairment of available-for-sale investments (Note 8)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -29330,11 +29318,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L228" s="5" t="n">
-        <v>0.54026</v>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>0.914944</v>
+        <v>0.007979999999999999</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -29385,14 +29375,10 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other comprehensive loss (income)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -29429,10 +29415,10 @@
         </is>
       </c>
       <c r="L229" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.01377</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.02719</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -29478,12 +29464,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Other Comprehensive loss (Income)</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Total 50,344 551,300 - 182,000 31,000 - 13,770 (554,030) 274,384 650,327 - 67,500 60,000 118,800 - (12,225) (7,980) (6,985)</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -29523,10 +29509,10 @@
         </is>
       </c>
       <c r="L230" s="5" t="n">
-        <v>0.256067</v>
+        <v>0.54026</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>-0.887754</v>
+        <v>0.914944</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -29572,15 +29558,19 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Other Comprehensive loss (Income)</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Warrants 128,600 188,000 (87,600) 229,000 182,000</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -29617,10 +29607,10 @@
         </is>
       </c>
       <c r="L231" s="5" t="n">
-        <v>0.37</v>
+        <v>2e-08</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>-0.041</v>
+        <v>3e-08</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -29666,12 +29656,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>of part Amount 9,980,438 551,300 (188,000) 182,000 10,525,738 650,327 (182,000) 81,500</t>
+          <t>Total 50,344 551,300 - 182,000 31,000 - 13,770 (554,030) 274,384 650,327 - 67,500 60,000 118,800 - (12,225) (7,980) (6,985)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -29711,10 +29701,10 @@
         </is>
       </c>
       <c r="L232" s="5" t="n">
-        <v>11.135565</v>
+        <v>0.256067</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.06</v>
+        <v>-0.887754</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -29760,12 +29750,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>$        $            $                                   Capital</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>of    - - - - -  -  - - - - - -                                                                                                                                                                                                                                                                                                                                                                                        integral an Share shares</t>
+          <t>Warrants 128,600 188,000 (87,600) 229,000 182,000</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -29805,10 +29795,10 @@
         </is>
       </c>
       <c r="L233" s="5" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="M233" s="5" t="n">
-        <v>0.675</v>
+        <v>-0.041</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -29854,12 +29844,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>$        $            $                                   Capital</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>are Number 15,432,961 7,965,666 2,600,000 25,998,627</t>
+          <t>of part Amount 9,980,438 551,300 (188,000) 182,000 10,525,738 650,327 (182,000) 81,500</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -29899,10 +29889,10 @@
         </is>
       </c>
       <c r="L234" s="5" t="n">
-        <v>34.258627</v>
+        <v>11.135565</v>
       </c>
       <c r="M234" s="5" t="n">
-        <v>6.835</v>
+        <v>0.06</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -29946,27 +29936,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>$        $            $                                   Capital</t>
+        </is>
+      </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>of    - - - - -  -  - - - - - -                                                                                                                                                                                                                                                                                                                                                                                        integral an Share shares</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F235" s="5" t="n">
-        <v>0.097347</v>
-      </c>
-      <c r="G235" s="5" t="n">
-        <v>0.16053</v>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -29983,16 +29977,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K235" s="5" t="n">
-        <v>0.0211</v>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L235" s="5" t="n">
-        <v>0.02844</v>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.75</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.675</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -30036,17 +30030,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>$        $            $                                   Capital</t>
+        </is>
+      </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>are Number 15,432,961 7,965,666 2,600,000 25,998,627</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -30057,11 +30051,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G236" s="5" t="n">
-        <v>0.000327</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>-0.001613</v>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -30073,16 +30071,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K236" s="5" t="n">
-        <v>0.000806</v>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L236" s="5" t="n">
-        <v>-0.000924</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>34.258627</v>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>6.835</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -30129,24 +30127,24 @@
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (recoveries) (Note 10)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Professional fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F237" s="5" t="n">
+        <v>0.097347</v>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>0.16053</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -30164,10 +30162,10 @@
         </is>
       </c>
       <c r="K237" s="5" t="n">
-        <v>-0.018583</v>
+        <v>0.0211</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>0.431295</v>
+        <v>0.02844</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -30219,10 +30217,14 @@
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Realized (gain) on marketable securities (Note 6)</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -30233,15 +30235,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G238" s="5" t="n">
+        <v>0.000327</v>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>-0.001613</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -30253,13 +30251,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" s="5" t="n">
+        <v>0.000806</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>-0.09868</v>
+        <v>-0.000924</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -30311,7 +30307,7 @@
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) on marketable securities (Note 6)</t>
+          <t>Exploration and evaluation expenditures (recoveries) (Note 10)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -30346,10 +30342,10 @@
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.018583</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>0.01</v>
+        <v>0.431295</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
@@ -30398,14 +30394,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Other Comprehensive (Income)</t>
-        </is>
-      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Change in unrealized gain on available-for-sale investments (Note 8)</t>
+          <t>Realized (gain) on marketable securities (Note 6)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -30434,14 +30426,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J240" s="5" t="n">
-        <v>-0.00414</v>
-      </c>
-      <c r="K240" s="5" t="n">
-        <v>-0.01228</v>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L240" s="5" t="n">
-        <v>-0.01377</v>
+        <v>-0.09868</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -30490,14 +30486,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Other Comprehensive (Income)</t>
-        </is>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Other comprehensive (income)</t>
+          <t>Unrealized loss (gain) on marketable securities (Note 6)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -30526,14 +30518,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J241" s="5" t="n">
-        <v>-0.00414</v>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>-0.01228</v>
+        <v>-0.01</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>-0.01377</v>
+        <v>0.01</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -30589,7 +30583,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Change in unrealized gain on available-for-sale investments (Note 8)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -30619,13 +30613,13 @@
         </is>
       </c>
       <c r="J242" s="5" t="n">
-        <v>0.272154</v>
+        <v>-0.00414</v>
       </c>
       <c r="K242" s="5" t="n">
-        <v>0.058658</v>
+        <v>-0.01228</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>0.54026</v>
+        <v>-0.01377</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -30681,14 +30675,10 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other comprehensive (income)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -30715,13 +30705,13 @@
         </is>
       </c>
       <c r="J243" s="5" t="n">
-        <v>3e-08</v>
+        <v>-0.00414</v>
       </c>
       <c r="K243" s="5" t="n">
-        <v>0</v>
+        <v>-0.01228</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.01377</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -30772,19 +30762,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
+          <t>Other Comprehensive (Income)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -30811,15 +30797,13 @@
         </is>
       </c>
       <c r="J244" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.272154</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.058658</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>0.54026</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -30870,17 +30854,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
+          <t>Other Comprehensive (Income)</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 11)</t>
+          <t>Loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -30909,15 +30893,13 @@
         </is>
       </c>
       <c r="J245" s="5" t="n">
-        <v>0.0375</v>
+        <v>3e-08</v>
       </c>
       <c r="K245" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -30973,10 +30955,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 13(c) and 15)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Professional fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -31002,13 +30988,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J246" s="5" t="n">
+        <v>0.0431</v>
       </c>
       <c r="K246" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0211</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -31069,10 +31053,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Premises</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Management and consulting fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -31093,16 +31081,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I247" s="5" t="n">
-        <v>0.009488999999999999</v>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J247" s="5" t="n">
-        <v>0.003952</v>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0375</v>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>0.024</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -31163,14 +31151,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Office, general and administration</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share based payments (Notes 13(c) and 15)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -31191,14 +31175,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n">
-        <v>0.034191</v>
-      </c>
-      <c r="J248" s="5" t="n">
-        <v>0.051445</v>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>0.020523</v>
+        <v>0.011</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -31259,7 +31247,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Promotion and travel</t>
+          <t>Premises</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -31284,13 +31272,15 @@
         </is>
       </c>
       <c r="I249" s="5" t="n">
-        <v>0.039976</v>
+        <v>0.009488999999999999</v>
       </c>
       <c r="J249" s="5" t="n">
-        <v>0.046925</v>
-      </c>
-      <c r="K249" s="5" t="n">
-        <v>0.022092</v>
+        <v>0.003952</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -31351,12 +31341,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Office, general and administration</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -31379,16 +31369,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I250" s="5" t="n">
+        <v>0.034191</v>
       </c>
       <c r="J250" s="5" t="n">
-        <v>8.2e-05</v>
+        <v>0.051445</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>0.000806</v>
+        <v>0.020523</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -31449,7 +31437,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Exploration and evaluation (recoveries) expenditures (Note 10)</t>
+          <t>Promotion and travel</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -31473,16 +31461,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I251" s="5" t="n">
+        <v>0.039976</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.08930299999999999</v>
+        <v>0.046925</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>-0.018583</v>
+        <v>0.022092</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -31543,10 +31529,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>CROWN MINING CORP. (formerly Crown Gold Corporation) total</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -31567,14 +31557,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I252" s="5" t="n">
-        <v>0.465389</v>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J252" s="5" t="n">
-        <v>0.272307</v>
+        <v>8.2e-05</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.080938</v>
+        <v>0.000806</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -31635,7 +31627,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 6)</t>
+          <t>Exploration and evaluation (recoveries) expenditures (Note 10)</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -31664,13 +31656,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J253" s="5" t="n">
+        <v>0.08930299999999999</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.018583</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -31731,7 +31721,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Interest on convertible debentures (Note 12)</t>
+          <t>CROWN MINING CORP. (formerly Crown Gold Corporation) total</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -31755,18 +31745,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I254" s="5" t="n">
+        <v>0.465389</v>
       </c>
       <c r="J254" s="5" t="n">
-        <v>0.003987</v>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.272307</v>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>0.080938</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -31827,14 +31813,10 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized gain on marketable securities (Note 6)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31855,14 +31837,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I255" s="5" t="n">
-        <v>-0.5401589999999999</v>
-      </c>
-      <c r="J255" s="5" t="n">
-        <v>-0.276294</v>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-0.070938</v>
+        <v>-0.01</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -31918,12 +31904,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares - basic and diluted (000’s) (1)</t>
+          <t>Interest on convertible debentures (Note 12)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -31947,14 +31933,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I256" s="5" t="n">
-        <v>0.009344999999999999</v>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J256" s="5" t="n">
-        <v>0.01091</v>
-      </c>
-      <c r="K256" s="5" t="n">
-        <v>0.014644</v>
+        <v>0.003987</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -32010,15 +32000,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Total (95,094) 293,250 - 24,000 - 4,140 (276,294) (49,998) 148,000 - 11,000 - 12,280</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32039,13 +32033,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I257" s="5" t="n">
+        <v>-0.5401589999999999</v>
       </c>
       <c r="J257" s="5" t="n">
-        <v>0.050344</v>
+        <v>-0.276294</v>
       </c>
       <c r="K257" s="5" t="n">
         <v>-0.070938</v>
@@ -32109,7 +32101,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>income Accumulated other comprehensive (loss) (3,000) - - - - 4,140 - 1,140 - - - - 12,280</t>
+          <t>Weighted average number of common shares - basic and diluted (000’s) (1)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -32133,18 +32125,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I258" s="5" t="n">
+        <v>0.009344999999999999</v>
       </c>
       <c r="J258" s="5" t="n">
-        <v>0.01342</v>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01091</v>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>0.014644</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -32205,7 +32193,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1. Warrants 21,000 87,000 600 108,600 41,000</t>
+          <t>Total (95,094) 293,250 - 24,000 - 4,140 (276,294) (49,998) 148,000 - 11,000 - 12,280</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -32235,10 +32223,10 @@
         </is>
       </c>
       <c r="J259" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.050344</v>
       </c>
       <c r="K259" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.070938</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -32294,12 +32282,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>of                                                                                                                                                2014.</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>of                                                                                                                                                2014. part Amount 9,643,588 293,250 (87,000) 24,200 (600) 9,873,438 148,000 (41,000)</t>
+          <t>income Accumulated other comprehensive (loss) (3,000) - - - - 4,140 - 1,140 - - - - 12,280</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -32329,10 +32317,12 @@
         </is>
       </c>
       <c r="J260" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="K260" s="5" t="n">
-        <v>9.980437999999999</v>
+        <v>0.01342</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -32388,19 +32378,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Professional fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>1. Warrants 21,000 87,000 600 108,600 41,000</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -32421,16 +32407,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I261" s="5" t="n">
-        <v>0.059661</v>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J261" s="5" t="n">
-        <v>0.0431</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1286</v>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>-0.021</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -32486,19 +32472,15 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
+          <t>of                                                                                                                                                2014.</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>of                                                                                                                                                2014. part Amount 9,643,588 293,250 (87,000) 24,200 (600) 9,873,438 148,000 (41,000)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -32519,16 +32501,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I262" s="5" t="n">
-        <v>0.06</v>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J262" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-05</v>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>9.980437999999999</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -32589,10 +32571,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Share based payments (Notes 10 and 12 (c))</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Professional fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -32614,12 +32600,10 @@
         </is>
       </c>
       <c r="I263" s="5" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.059661</v>
+      </c>
+      <c r="J263" s="5" t="n">
+        <v>0.0431</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -32685,12 +32669,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
+          <t>Management and consulting fees (Note 10)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -32714,10 +32698,10 @@
         </is>
       </c>
       <c r="I264" s="5" t="n">
-        <v>-0.001046</v>
+        <v>0.06</v>
       </c>
       <c r="J264" s="5" t="n">
-        <v>8.2e-05</v>
+        <v>0.0375</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -32783,7 +32767,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Notes 9 and 10)</t>
+          <t>Share based payments (Notes 10 and 12 (c))</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -32808,10 +32792,12 @@
         </is>
       </c>
       <c r="I265" s="5" t="n">
-        <v>0.245118</v>
-      </c>
-      <c r="J265" s="5" t="n">
-        <v>0.08930299999999999</v>
+        <v>0.018</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -32877,10 +32863,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Interest on convertible debentures (Note 11)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -32902,10 +32892,10 @@
         </is>
       </c>
       <c r="I266" s="5" t="n">
-        <v>0.004063</v>
+        <v>-0.001046</v>
       </c>
       <c r="J266" s="5" t="n">
-        <v>0.003987</v>
+        <v>8.2e-05</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -32971,7 +32961,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 12 (a))</t>
+          <t>Exploration and evaluation expenditures (Notes 9 and 10)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -32996,12 +32986,10 @@
         </is>
       </c>
       <c r="I267" s="5" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.245118</v>
+      </c>
+      <c r="J267" s="5" t="n">
+        <v>0.08930299999999999</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -33067,7 +33055,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 7)</t>
+          <t>Interest on convertible debentures (Note 11)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -33092,12 +33080,10 @@
         </is>
       </c>
       <c r="I268" s="5" t="n">
-        <v>0.06933</v>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004063</v>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>0.003987</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -33163,7 +33149,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Loss on sale of available-for-sale investments (Note 7)</t>
+          <t>Flow-through share premium recovery (Note 12 (a))</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -33188,7 +33174,7 @@
         </is>
       </c>
       <c r="I269" s="5" t="n">
-        <v>0.007377</v>
+        <v>-0.006</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -33254,12 +33240,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Other Comprehensive (Income) Loss</t>
+          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Change in unrealized loss on available-for-sale investments (Note 7)</t>
+          <t>Impairment of available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -33284,10 +33270,12 @@
         </is>
       </c>
       <c r="I270" s="5" t="n">
-        <v>0.06124</v>
-      </c>
-      <c r="J270" s="5" t="n">
-        <v>-0.00414</v>
+        <v>0.06933</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -33348,12 +33336,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Other Comprehensive (Income) Loss</t>
+          <t>CROWN MINING CORP. (formerly Crown Gold Corporation)</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Impairment of available-for-sale investments (Note 7)</t>
+          <t>Loss on sale of available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -33378,7 +33366,7 @@
         </is>
       </c>
       <c r="I271" s="5" t="n">
-        <v>-0.06933</v>
+        <v>0.007377</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -33449,7 +33437,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Change in unrealized loss on available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -33474,7 +33462,7 @@
         </is>
       </c>
       <c r="I272" s="5" t="n">
-        <v>-0.00809</v>
+        <v>0.06124</v>
       </c>
       <c r="J272" s="5" t="n">
         <v>-0.00414</v>
@@ -33543,7 +33531,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Impairment of available-for-sale investments (Note 7)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -33568,10 +33556,12 @@
         </is>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0.532069</v>
-      </c>
-      <c r="J273" s="5" t="n">
-        <v>0.272154</v>
+        <v>-0.06933</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -33637,14 +33627,10 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -33655,17 +33641,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="H274" s="5" t="n">
-        <v>1e-08</v>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I274" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>-0.00809</v>
       </c>
       <c r="J274" s="5" t="n">
-        <v>3e-08</v>
+        <v>-0.00414</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -33724,17 +33714,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Other Comprehensive (Income) Loss</t>
+        </is>
+      </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Professional fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -33745,21 +33735,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G275" s="5" t="n">
-        <v>0.16053</v>
-      </c>
-      <c r="H275" s="5" t="n">
-        <v>0.070081</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>0.532069</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>0.272154</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -33818,13 +33808,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Other Comprehensive (Income) Loss</t>
+        </is>
+      </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Share based payments (Note 11 (b))</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -33836,20 +33834,16 @@
         </is>
       </c>
       <c r="G276" s="5" t="n">
-        <v>0.025</v>
+        <v>2e-08</v>
       </c>
       <c r="H276" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-08</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="J276" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -33911,23 +33905,29 @@
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Premises</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Professional fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F277" s="5" t="n">
-        <v>0.014869</v>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>0.037995</v>
+        <v>0.16053</v>
       </c>
       <c r="H277" s="5" t="n">
-        <v>0.021031</v>
+        <v>0.070081</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Promotion and travel</t>
+          <t>Share based payments (Note 11 (b))</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -34008,14 +34008,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F278" s="5" t="n">
-        <v>0.07745299999999999</v>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>0.065154</v>
+        <v>0.025</v>
       </c>
       <c r="H278" s="5" t="n">
-        <v>0.040661</v>
+        <v>0.024</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -34087,29 +34089,23 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Premises</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F279" s="5" t="n">
-        <v>0.000763</v>
+        <v>0.014869</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>0.007856</v>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037995</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.021031</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -34181,7 +34177,7 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Flow-through share premium recovery (Note 11 (a))</t>
+          <t>Promotion and travel</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -34190,18 +34186,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F280" s="5" t="n">
+        <v>0.07745299999999999</v>
+      </c>
+      <c r="G280" s="5" t="n">
+        <v>0.065154</v>
       </c>
       <c r="H280" s="5" t="n">
-        <v>-0.161</v>
+        <v>0.040661</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -34273,27 +34265,29 @@
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Impairment of investments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="n">
-        <v>0.289083</v>
+      <c r="F281" s="5" t="n">
+        <v>0.000763</v>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>0.007856</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -34365,7 +34359,7 @@
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Gain on sale of subsidiary (Note 14)</t>
+          <t>Flow-through share premium recovery (Note 11 (a))</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -34385,7 +34379,7 @@
         </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>-1e-05</v>
+        <v>-0.161</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -34454,14 +34448,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Write-down (Recovery) of exploration and evaluation</t>
-        </is>
-      </c>
+      <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Write-down (Recovery) of exploration and evaluation expenditures (Note 9)</t>
+          <t>Impairment of investments (Note 7)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -34475,11 +34465,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G283" s="5" t="n">
-        <v>0.613826</v>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H283" s="5" t="n">
-        <v>-0.1298</v>
+        <v>0.289083</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -34548,21 +34540,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Write-down (Recovery) of exploration and evaluation</t>
-        </is>
-      </c>
+      <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of subsidiary (Note 14)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -34573,11 +34557,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G284" s="5" t="n">
-        <v>-1.897481</v>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H284" s="5" t="n">
-        <v>-1.009537</v>
+        <v>-1e-05</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -34648,12 +34634,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Other Comprehensive (Income) Loss</t>
+          <t>Write-down (Recovery) of exploration and evaluation</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Change in unrealized loss on investments (Note 7)</t>
+          <t>Write-down (Recovery) of exploration and evaluation expenditures (Note 9)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -34668,10 +34654,10 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>0.22524</v>
+        <v>0.613826</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>-0.03671</v>
+        <v>-0.1298</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -34742,15 +34728,19 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Other Comprehensive (Income) Loss</t>
+          <t>Write-down (Recovery) of exploration and evaluation</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Impairment of investments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -34761,13 +34751,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G286" s="5" t="n">
+        <v>-1.897481</v>
       </c>
       <c r="H286" s="5" t="n">
-        <v>-0.289083</v>
+        <v>-1.009537</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -34843,7 +34831,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign subsidiary</t>
+          <t>Change in unrealized loss on investments (Note 7)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -34858,10 +34846,10 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>-0.000933</v>
+        <v>0.22524</v>
       </c>
       <c r="H287" s="5" t="n">
-        <v>0.002674</v>
+        <v>-0.03671</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -34937,7 +34925,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Other comprehensive (income) loss</t>
+          <t>Impairment of investments (Note 7)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -34951,11 +34939,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G288" s="5" t="n">
-        <v>0.224307</v>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H288" s="5" t="n">
-        <v>-0.323119</v>
+        <v>-0.289083</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -35031,7 +35021,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Exchange difference on translation of foreign subsidiary</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -35046,10 +35036,10 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>2.121788</v>
+        <v>-0.000933</v>
       </c>
       <c r="H289" s="5" t="n">
-        <v>0.686418</v>
+        <v>0.002674</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -35118,32 +35108,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Other Comprehensive (Income) Loss</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Management and consulting fees</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Other comprehensive (income) loss</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F290" s="5" t="n">
-        <v>0.067062</v>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G290" s="5" t="n">
-        <v>0.10564</v>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.224307</v>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>-0.323119</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -35212,10 +35202,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Other Comprehensive (Income) Loss</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Share based payments (Note 12 (c))</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -35224,16 +35218,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F291" s="5" t="n">
-        <v>0.106</v>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.121788</v>
+      </c>
+      <c r="H291" s="5" t="n">
+        <v>0.686418</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -35305,22 +35299,24 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Part XII.6 tax</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
+          <t>Management and consulting fees</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.001344</v>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.067062</v>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>0.10564</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -35397,24 +35393,20 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share based payments (Note 12 (c))</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F293" s="5" t="n">
-        <v>0.014177</v>
+        <v>0.106</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>0.000327</v>
+        <v>0.025</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -35491,7 +35483,7 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve"> total</t>
+          <t>Part XII.6 tax</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -35501,10 +35493,12 @@
         </is>
       </c>
       <c r="F294" s="5" t="n">
-        <v>1.201646</v>
-      </c>
-      <c r="G294" s="5" t="n">
-        <v>1.283655</v>
+        <v>0.001344</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -35581,22 +35575,24 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Acquisition related costs (Note 20)</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F295" s="5" t="n">
-        <v>0.330663</v>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014177</v>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>0.000327</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -35670,14 +35666,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Write-down of exploration and evaluation</t>
-        </is>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation expenditures (Note 9)</t>
+          <t xml:space="preserve"> total</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -35686,13 +35678,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F296" s="5" t="n">
+        <v>1.201646</v>
       </c>
       <c r="G296" s="5" t="n">
-        <v>0.613826</v>
+        <v>1.283655</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -35766,31 +35756,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Write-down of exploration and evaluation</t>
-        </is>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Acquisition related costs (Note 20)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F297" s="5" t="n">
-        <v>-1.532309</v>
-      </c>
-      <c r="G297" s="5" t="n">
-        <v>-1.897481</v>
+        <v>0.330663</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -35871,24 +35855,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-down of exploration and evaluation expenditures (Note 9)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F298" s="5" t="n">
-        <v>3e-08</v>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G298" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.613826</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -35964,25 +35946,29 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Write-down of exploration and evaluation</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Weighted average number total</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F299" s="5" t="n">
-        <v>47.518708</v>
+        <v>-1.532309</v>
       </c>
       <c r="G299" s="5" t="n">
-        <v>83.83345199999999</v>
+        <v>-1.897481</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -36058,25 +36044,29 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Write-down of exploration and evaluation</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Change in unrealized loss on investments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F300" s="5" t="n">
-        <v>0.111643</v>
+        <v>3e-08</v>
       </c>
       <c r="G300" s="5" t="n">
-        <v>0.22524</v>
+        <v>2e-08</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -36152,12 +36142,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign subsidiary</t>
+          <t>Weighted average number total</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -36167,10 +36157,10 @@
         </is>
       </c>
       <c r="F301" s="5" t="n">
-        <v>-0.001741</v>
+        <v>47.518708</v>
       </c>
       <c r="G301" s="5" t="n">
-        <v>-0.000933</v>
+        <v>83.83345199999999</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -36251,7 +36241,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Change in unrealized loss on investments (Note 7)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -36261,10 +36251,10 @@
         </is>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.109902</v>
+        <v>0.111643</v>
       </c>
       <c r="G302" s="5" t="n">
-        <v>0.224307</v>
+        <v>0.22524</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -36345,24 +36335,20 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Net Loss</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Exchange difference on translation of foreign subsidiary</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F303" s="5" t="n">
-        <v>-1.532309</v>
+        <v>-0.001741</v>
       </c>
       <c r="G303" s="5" t="n">
-        <v>-1.897481</v>
+        <v>-0.000933</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -36443,7 +36429,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Comprehensive loss 2,121,788</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -36453,10 +36439,10 @@
         </is>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.000211</v>
+        <v>0.109902</v>
       </c>
       <c r="G304" s="5" t="n">
-        <v>0.001642</v>
+        <v>0.224307</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -36537,17 +36523,21 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Total 260,292 1,645,912 8,057 90,800 - - - 5,358,215 106,000 (111,643) 1,741 (1,532,309) 5,827,065 80,469 502,500 - - 25,000 933 (225,240)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>Net Loss</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F305" s="5" t="n">
-        <v>4.313246</v>
+        <v>-1.532309</v>
       </c>
       <c r="G305" s="5" t="n">
         <v>-1.897481</v>
@@ -36631,7 +36621,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-- - - -      - - - - - -   - - -                                                                                                                                                                                                                                                                                                                                                                                                                                                            statements based payments 226,393 138,000 106,000 470,393 558,855</t>
+          <t>Comprehensive loss 2,121,788</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -36641,10 +36631,10 @@
         </is>
       </c>
       <c r="F306" s="5" t="n">
-        <v>1.054248</v>
+        <v>0.000211</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>0.025</v>
+        <v>0.001642</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -36720,29 +36710,25 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11) $</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E307" s="5" t="n">
-        <v>0.058776</v>
+          <t>Total 260,292 1,645,912 8,057 90,800 - - - 5,358,215 106,000 (111,643) 1,741 (1,532,309) 5,827,065 80,469 502,500 - - 25,000 933 (225,240)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F307" s="5" t="n">
-        <v>0.097347</v>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.313246</v>
+      </c>
+      <c r="G307" s="5" t="n">
+        <v>-1.897481</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -36818,29 +36804,25 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E308" s="5" t="n">
-        <v>0.03</v>
+          <t>-- - - -      - - - - - -   - - -                                                                                                                                                                                                                                                                                                                                                                                                                                                            statements based payments 226,393 138,000 106,000 470,393 558,855</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.067062</v>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.054248</v>
+      </c>
+      <c r="G308" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -36921,17 +36903,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 9 (c))</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees (Note 11) $</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>0.058776</v>
       </c>
       <c r="F309" s="5" t="n">
-        <v>0.106</v>
+        <v>0.097347</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -37017,15 +37001,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Premises</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Management and consulting fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
-        <v>0.014077</v>
+        <v>0.03</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.014869</v>
+        <v>0.067062</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -37111,19 +37099,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Office, general and administration</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E311" s="5" t="n">
-        <v>0.031419</v>
+          <t>Stock-based compensation (Note 9 (c))</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F311" s="5" t="n">
-        <v>0.096114</v>
+        <v>0.106</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -37209,15 +37195,15 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Promotion and travel</t>
+          <t>Premises</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" s="5" t="n">
-        <v>0.029014</v>
+        <v>0.014077</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.07745299999999999</v>
+        <v>0.014869</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -37303,15 +37289,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Part XII.6 tax</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Office, general and administration</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E313" s="5" t="n">
-        <v>0.010266</v>
+        <v>0.031419</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>0.001344</v>
+        <v>0.096114</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -37397,21 +37387,15 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Promotion and travel</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" s="5" t="n">
+        <v>0.029014</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>0.009613</v>
+        <v>0.07745299999999999</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37497,21 +37481,15 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Part XII.6 tax</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" s="5" t="n">
+        <v>0.010266</v>
       </c>
       <c r="F315" s="5" t="n">
-        <v>0.000763</v>
+        <v>0.001344</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -37597,19 +37575,21 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E316" s="5" t="n">
-        <v>0.173552</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F316" s="5" t="n">
-        <v>0.470565</v>
+        <v>0.009613</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -37695,15 +37675,21 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Loss before the undernoted</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" s="5" t="n">
-        <v>-0.173552</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F317" s="5" t="n">
-        <v>-0.470565</v>
+        <v>0.000763</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -37789,17 +37775,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Acquisition related costs (Note 5)</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="n">
+        <v>0.173552</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.330663</v>
+        <v>0.470565</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -37885,17 +37873,15 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral properties</t>
+          <t>Loss before the undernoted</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E319" s="5" t="n">
+        <v>-0.173552</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>0.060266</v>
+        <v>-0.470565</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -37981,7 +37967,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>(Note 8)</t>
+          <t>Acquisition related costs (Note 5)</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -37991,7 +37977,7 @@
         </is>
       </c>
       <c r="F320" s="5" t="n">
-        <v>-0.413664</v>
+        <v>-0.330663</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -38077,15 +38063,17 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Loss before taxes</t>
+          <t>Gain on disposal of mineral properties</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" s="5" t="n">
-        <v>-0.173552</v>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F321" s="5" t="n">
-        <v>-1.154626</v>
+        <v>0.060266</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -38171,15 +38159,17 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Future income tax recovery (Note 12)</t>
+          <t>(Note 8)</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
-      <c r="E322" s="5" t="n">
-        <v>0.006</v>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.078</v>
+        <v>-0.413664</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -38265,19 +38255,15 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss before taxes</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" s="5" t="n">
-        <v>-0.167552</v>
+        <v>-0.173552</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>-1.076626</v>
+        <v>-1.154626</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -38363,15 +38349,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Future income tax recovery (Note 12)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E324" s="5" t="n">
-        <v>-0.401585</v>
+        <v>0.006</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>-0.569137</v>
+        <v>0.078</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -38457,15 +38447,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Deficit, end of year</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E325" s="5" t="n">
-        <v>-0.569137</v>
+        <v>-0.167552</v>
       </c>
       <c r="F325" s="5" t="n">
-        <v>-1.645763</v>
+        <v>-1.076626</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -38551,15 +38545,15 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Loss per share-basic and fully diluted $</t>
+          <t>Deficit, beginning of year</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
       <c r="E326" s="5" t="n">
-        <v>-7e-09</v>
+        <v>-0.401585</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-2.3e-08</v>
+        <v>-0.569137</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -38645,86 +38639,274 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
+          <t>Deficit, end of year</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" s="5" t="n">
+        <v>-0.569137</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>-1.645763</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Loss per share-basic and fully diluted $</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" s="5" t="n">
+        <v>-7e-09</v>
+      </c>
+      <c r="F328" s="5" t="n">
+        <v>-2.3e-08</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E327" s="5" t="n">
+      <c r="E329" s="5" t="n">
         <v>24.003285</v>
       </c>
-      <c r="F327" s="5" t="n">
+      <c r="F329" s="5" t="n">
         <v>47.518708</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T327" t="inlineStr">
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
         <is>
           <t>-</t>
         </is>
